--- a/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250606103858</t>
+    <t>20250611134353</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-06T10:38:58+01:00</t>
+    <t>2025-06-11T13:43:53+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250611134353</t>
+    <t>20250616134740</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T13:43:53+01:00</t>
+    <t>2025-06-16T13:47:40+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250616134740</t>
+    <t>20250624152100</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T13:47:40+01:00</t>
+    <t>2025-06-24T15:21:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250624152100</t>
+    <t>20251028115834</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T15:21:00+01:00</t>
+    <t>2025-10-28T11:58:34+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251028115834</t>
+    <t>20251216141839</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T11:58:34+01:00</t>
+    <t>2025-12-16T14:18:39+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141839</t>
+    <t>20260220142104</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:39+01:00</t>
+    <t>2026-02-20T14:21:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142104</t>
+    <t>20260311144904</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:04+01:00</t>
+    <t>2026-03-11T14:49:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144904</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:04+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,19 +120,19 @@
     <t>30428-7</t>
   </si>
   <si>
-    <t>Volume globulaire moyen [Volume d'entité] Érythrocytes ; Numérique</t>
+    <t>Observation [Volume moyen de l'entité] Érythrocytes ; Numérique</t>
   </si>
   <si>
     <t>28540-3</t>
   </si>
   <si>
-    <t>Concentration corpusculaire moyenne en hémoglobine [Masse/Volume] Érythrocytes ; Numérique</t>
+    <t>Hémoglobine [Masse/Volume de l'entité] Érythrocytes ; Numérique</t>
   </si>
   <si>
     <t>28539-5</t>
   </si>
   <si>
-    <t>Teneur corpusculaire moyenne en hémoglobine [Masse d'entité] Érythrocytes ; Numérique</t>
+    <t>Hémoglobine [Masse d'entité] Érythrocytes ; Numérique</t>
   </si>
   <si>
     <t>777-3</t>
@@ -150,31 +150,31 @@
     <t>26511-6</t>
   </si>
   <si>
-    <t>Polynucléaires neutrophiles/100 leucocytes [Fraction de nombres] Sang ; Numérique</t>
+    <t>Polynucléaires neutrophiles/leucocytes [Fraction de nombres] Sang ; Numérique</t>
   </si>
   <si>
     <t>26450-7</t>
   </si>
   <si>
-    <t>Polynucléaires éosinophiles/100 leucocytes [Fraction de nombres] Sang ; Numérique</t>
+    <t>Polynucléaires éosinophiles/leucocytes [Fraction de nombres] Sang ; Numérique</t>
   </si>
   <si>
     <t>30180-4</t>
   </si>
   <si>
-    <t>Polynucléaires basophiles/100 leucocytes [Fraction de nombres] Sang ; Numérique</t>
+    <t>Polynucléaires basophiles/leucocytes [Fraction de nombres] Sang ; Numérique</t>
   </si>
   <si>
     <t>26478-8</t>
   </si>
   <si>
-    <t>Lymphocytes totaux/100 leucocytes [Fraction de nombres] Sang ; Numérique</t>
+    <t>Lymphocytes totaux/leucocytes [Fraction de nombres] Sang ; Numérique</t>
   </si>
   <si>
     <t>26485-3</t>
   </si>
   <si>
-    <t>Monocytes/100 leucocytes [Fraction de nombres] Sang ; Numérique</t>
+    <t>Monocytes/leucocytes [Fraction de nombres] Sang ; Numérique</t>
   </si>
   <si>
     <t/>

--- a/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-examen-hematologie-aunv-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150251</t>
+    <t>20260619134042</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:51+01:00</t>
+    <t>2026-06-19T13:40:42+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
